--- a/GMAB.xlsx
+++ b/GMAB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1269D71-57F6-472E-A614-5F994ABFDD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6191F1-0CE0-407B-806D-19A674E8B67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14120" yWindow="3850" windowWidth="22760" windowHeight="13530" activeTab="1" xr2:uid="{0D5CB397-B169-4B4B-B34C-77A7CB149699}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{0D5CB397-B169-4B4B-B34C-77A7CB149699}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
   <si>
     <t>Name</t>
   </si>
@@ -153,12 +153,6 @@
     <t>Tecvayli (teclistamab)</t>
   </si>
   <si>
-    <t>Cash DKK</t>
-  </si>
-  <si>
-    <t>Debt DKK</t>
-  </si>
-  <si>
     <t>EV DKK</t>
   </si>
   <si>
@@ -232,16 +226,32 @@
   </si>
   <si>
     <t>Other Revenue</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Cash USD</t>
+  </si>
+  <si>
+    <t>Debt USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -349,10 +359,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -367,8 +378,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -719,7 +732,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="11">
-        <v>20.74</v>
+        <v>28.87</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -739,8 +752,8 @@
       <c r="J3" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="1">
-        <v>1375</v>
+      <c r="K3" s="11">
+        <v>1858</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -761,10 +774,10 @@
         <v>15</v>
       </c>
       <c r="K4" s="1">
-        <v>66.197243999999998</v>
+        <v>64.243333000000007</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -780,7 +793,7 @@
       </c>
       <c r="K5" s="1">
         <f>+K2*K4*10</f>
-        <v>13729.308405599997</v>
+        <v>18547.050237100004</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -796,7 +809,7 @@
       </c>
       <c r="K6" s="1">
         <f>+K3*K4</f>
-        <v>91021.210500000001</v>
+        <v>119364.11271400002</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -808,11 +821,14 @@
       </c>
       <c r="H7" s="4"/>
       <c r="J7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="K7" s="1">
+        <f>1521+40</f>
+        <v>1561</v>
+      </c>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -824,11 +840,14 @@
       </c>
       <c r="H8" s="4"/>
       <c r="J8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="K8" s="1">
+        <f>4933+275</f>
+        <v>5208</v>
+      </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
@@ -840,19 +859,19 @@
       <c r="G9" s="9"/>
       <c r="H9" s="10"/>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K9" s="1">
         <f>+K6-K7+K8</f>
-        <v>91021.210500000001</v>
+        <v>123011.11271400002</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -912,7 +931,7 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H15" s="4"/>
     </row>
@@ -936,38 +955,39 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>45</v>
+      <c r="A1" s="12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="M2">
         <v>2022</v>
@@ -987,7 +1007,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P3">
         <v>13000</v>
@@ -995,7 +1015,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P4">
         <v>2200</v>
@@ -1003,7 +1023,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P5">
         <v>700</v>
@@ -1011,7 +1031,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2">
         <v>452</v>
@@ -1026,7 +1046,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P7">
         <f>438+162</f>
@@ -1035,7 +1055,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2">
         <v>603</v>
@@ -1050,7 +1070,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2">
         <v>27</v>
@@ -1061,7 +1081,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2">
         <f>+C8-C9</f>
@@ -1074,7 +1094,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C11" s="2">
         <v>335</v>
@@ -1085,7 +1105,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2">
         <v>125</v>
@@ -1096,7 +1116,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:F13" si="0">+C11+C12</f>
@@ -1121,7 +1141,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2">
         <f t="shared" ref="C14:F14" si="1">+C10-C13</f>
@@ -1145,6 +1165,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{F2C1126B-F77A-4486-A9EA-03BC0530FDAF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>